--- a/derivatives/BAR/P9214_preprocessed.xlsx
+++ b/derivatives/BAR/P9214_preprocessed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>listno</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>trialno</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>conceptno</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>concept</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>concept_HU</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>responded</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>response_HU</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>similarity</t>
         </is>
@@ -1303,7 +1315,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0.4532738029956818</v>
+        <v>0.4532738924026489</v>
       </c>
     </row>
     <row r="21">
@@ -1869,7 +1881,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.2082509845495224</v>
+        <v>0.2082509547472</v>
       </c>
     </row>
     <row r="34">
@@ -2875,7 +2887,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0.2643619477748871</v>
+        <v>0.2643620073795319</v>
       </c>
     </row>
     <row r="57">
@@ -2969,7 +2981,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0.4741913080215454</v>
+        <v>0.4741913378238678</v>
       </c>
     </row>
     <row r="59">
@@ -3189,7 +3201,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.58611661195755</v>
+        <v>0.5861166715621948</v>
       </c>
     </row>
     <row r="64">
@@ -3923,7 +3935,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.3222156465053558</v>
+        <v>0.3222156763076782</v>
       </c>
     </row>
     <row r="81">
@@ -3975,7 +3987,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.764471173286438</v>
+        <v>0.7644711136817932</v>
       </c>
     </row>
     <row r="82">
@@ -4541,7 +4553,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0.4413833022117615</v>
+        <v>0.4413832426071167</v>
       </c>
     </row>
     <row r="95">
@@ -4593,7 +4605,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0.3156337738037109</v>
+        <v>0.3156337440013885</v>
       </c>
     </row>
     <row r="96">
@@ -4645,7 +4657,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0.5923802852630615</v>
+        <v>0.5923803448677063</v>
       </c>
     </row>
     <row r="97">
